--- a/output/pdf_financials_xlsx/PREV.xlsx
+++ b/output/pdf_financials_xlsx/PREV.xlsx
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.82788</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.830829</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.010513</v>
       </c>
     </row>
     <row r="93">
@@ -2089,13 +2089,13 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.018472</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.026264</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.026489</v>
       </c>
     </row>
     <row r="104">
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.545677</v>
+        <v>0.527205</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.316689</v>
+        <v>0.342953</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.933226</v>
+        <v>0.906737</v>
       </c>
     </row>
     <row r="107">
@@ -2751,7 +2751,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="n">
         <v>0.056992</v>
       </c>
@@ -3303,7 +3307,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>1.82788</v>
       </c>
@@ -3859,7 +3867,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>-0.018472</v>
       </c>

--- a/output/pdf_financials_xlsx/PREV.xlsx
+++ b/output/pdf_financials_xlsx/PREV.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.26584</v>
+        <v>0.963124</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.371435</v>
+        <v>0.812466</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.065709</v>
+        <v>3.367111</v>
       </c>
     </row>
     <row r="11">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.001432</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.059139</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.010239</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.001432</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.059139</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.010239</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.058424</v>
+        <v>0.056992</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.08988500000000001</v>
+        <v>0.030746</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.058764</v>
+        <v>1.048525</v>
       </c>
     </row>
     <row r="49">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">

--- a/output/pdf_financials_xlsx/PREV.xlsx
+++ b/output/pdf_financials_xlsx/PREV.xlsx
@@ -4024,7 +4024,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
